--- a/hairdresser_forms/013_tape_in_hair_extension_placement_checklist--hairdresser_forms.xlsx
+++ b/hairdresser_forms/013_tape_in_hair_extension_placement_checklist--hairdresser_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'fine'}</t>
+          <t>fine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Fine'}</t>
+          <t>Fine</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'coarse'}</t>
+          <t>coarse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Coarse'}</t>
+          <t>Coarse</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'clip-in'}</t>
+          <t>clip-in</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Clip-in'}</t>
+          <t>Clip-in</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'tape-in'}</t>
+          <t>tape-in</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Tape-in'}</t>
+          <t>Tape-in</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'micro-link'}</t>
+          <t>micro-link</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Micro-link'}</t>
+          <t>Micro-link</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'short'}</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Short'}</t>
+          <t>Short</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'long'}</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Long'}</t>
+          <t>Long</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'blonde'}</t>
+          <t>blonde</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Blonde'}</t>
+          <t>Blonde</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'brown'}</t>
+          <t>brown</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Brown'}</t>
+          <t>Brown</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
